--- a/Codex Wheat.xlsx
+++ b/Codex Wheat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\grain-data-intelligence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF3EE52-676B-454E-9CB8-417357F316CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A9CB6D-31C6-40B9-B608-74DF9875CE9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28980" yWindow="0" windowWidth="29040" windowHeight="15720" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
+    <workbookView xWindow="28530" yWindow="-16440" windowWidth="29040" windowHeight="15720" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
   </bookViews>
   <sheets>
     <sheet name="Wheat" sheetId="7" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="430">
   <si>
     <t>2024/25</t>
   </si>
@@ -1323,6 +1323,9 @@
   </si>
   <si>
     <t>22/08 - 28/08/2026</t>
+  </si>
+  <si>
+    <t>29/08 - 04/09/2026</t>
   </si>
 </sst>
 </file>
@@ -1333,7 +1336,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1376,6 +1379,11 @@
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Narrow"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1554,7 +1562,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1838,7 +1846,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76B85704-FA9F-47C9-8710-67621FBDF428}">
-  <dimension ref="A1:N414"/>
+  <dimension ref="A1:N415"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -10188,14 +10196,34 @@
       <c r="C414" s="20" t="s">
         <v>428</v>
       </c>
-      <c r="D414" s="21">
+      <c r="D414" s="19">
         <v>1030</v>
       </c>
-      <c r="E414" s="21">
-        <v>0</v>
-      </c>
-      <c r="F414" s="21">
-        <v>1030</v>
+      <c r="E414" s="19">
+        <v>10</v>
+      </c>
+      <c r="F414" s="19">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A415" s="1">
+        <v>49</v>
+      </c>
+      <c r="B415" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C415" s="21" t="s">
+        <v>429</v>
+      </c>
+      <c r="D415" s="19">
+        <v>323</v>
+      </c>
+      <c r="E415" s="19">
+        <v>0</v>
+      </c>
+      <c r="F415" s="19">
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -10205,14 +10233,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ae149517-eeaa-465d-b3b6-396a1e23bc6e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10443,21 +10469,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ae149517-eeaa-465d-b3b6-396a1e23bc6e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929ACA6-317A-4DC6-98B5-19C43F6EFDF0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
-    <ds:schemaRef ds:uri="ae149517-eeaa-465d-b3b6-396a1e23bc6e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10482,9 +10507,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929ACA6-317A-4DC6-98B5-19C43F6EFDF0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
+    <ds:schemaRef ds:uri="ae149517-eeaa-465d-b3b6-396a1e23bc6e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Codex Wheat.xlsx
+++ b/Codex Wheat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\grain-data-intelligence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A9CB6D-31C6-40B9-B608-74DF9875CE9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC418B1-975C-4D69-A61C-9497EAE589CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28530" yWindow="-16440" windowWidth="29040" windowHeight="15720" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
   </bookViews>
   <sheets>
     <sheet name="Wheat" sheetId="7" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="436">
   <si>
     <t>2024/25</t>
   </si>
@@ -1326,6 +1326,24 @@
   </si>
   <si>
     <t>29/08 - 04/09/2026</t>
+  </si>
+  <si>
+    <t>05/09 - 11/09/2026</t>
+  </si>
+  <si>
+    <t>12/09 - 18/09/2026</t>
+  </si>
+  <si>
+    <t>19/09 - 25/09/2026</t>
+  </si>
+  <si>
+    <t>2026/27</t>
+  </si>
+  <si>
+    <t>26/09 - 02/10/2026</t>
+  </si>
+  <si>
+    <t>03/10 - 09/10/2026</t>
   </si>
 </sst>
 </file>
@@ -1336,7 +1354,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1379,11 +1397,6 @@
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial Narrow"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1526,7 +1539,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1562,7 +1575,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1846,7 +1861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76B85704-FA9F-47C9-8710-67621FBDF428}">
-  <dimension ref="A1:N415"/>
+  <dimension ref="A1:N420"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -2113,7 +2128,12 @@
       <c r="F10" s="3">
         <v>144899</v>
       </c>
-      <c r="L10" s="8"/>
+      <c r="K10" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="L10" s="7">
+        <v>1805720</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -9900,10 +9920,10 @@
         <v>741</v>
       </c>
       <c r="E399" s="19">
-        <v>645</v>
+        <v>434</v>
       </c>
       <c r="F399" s="19">
-        <v>1386</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
@@ -9920,10 +9940,10 @@
         <v>1791</v>
       </c>
       <c r="E400" s="19">
-        <v>397</v>
+        <v>257</v>
       </c>
       <c r="F400" s="19">
-        <v>2188</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
@@ -10000,10 +10020,10 @@
         <v>1695</v>
       </c>
       <c r="E404" s="19">
-        <v>-62</v>
+        <v>-97</v>
       </c>
       <c r="F404" s="19">
-        <v>1633</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
@@ -10140,10 +10160,10 @@
         <v>811</v>
       </c>
       <c r="E411" s="19">
-        <v>0</v>
+        <v>-111</v>
       </c>
       <c r="F411" s="19">
-        <v>811</v>
+        <v>700</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
@@ -10160,10 +10180,10 @@
         <v>1090</v>
       </c>
       <c r="E412" s="19">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="F412" s="19">
-        <v>1090</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
@@ -10180,10 +10200,10 @@
         <v>1100</v>
       </c>
       <c r="E413" s="19">
-        <v>0</v>
+        <v>-49</v>
       </c>
       <c r="F413" s="19">
-        <v>1100</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
@@ -10193,17 +10213,17 @@
       <c r="B414" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C414" s="20" t="s">
+      <c r="C414" s="18" t="s">
         <v>428</v>
       </c>
       <c r="D414" s="19">
         <v>1030</v>
       </c>
       <c r="E414" s="19">
-        <v>10</v>
+        <v>248</v>
       </c>
       <c r="F414" s="19">
-        <v>1040</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
@@ -10213,7 +10233,7 @@
       <c r="B415" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C415" s="21" t="s">
+      <c r="C415" s="18" t="s">
         <v>429</v>
       </c>
       <c r="D415" s="19">
@@ -10224,6 +10244,106 @@
       </c>
       <c r="F415" s="19">
         <v>323</v>
+      </c>
+    </row>
+    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A416" s="1">
+        <v>50</v>
+      </c>
+      <c r="B416" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C416" s="18" t="s">
+        <v>430</v>
+      </c>
+      <c r="D416" s="19">
+        <v>317</v>
+      </c>
+      <c r="E416" s="19">
+        <v>0</v>
+      </c>
+      <c r="F416" s="19">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A417" s="1">
+        <v>51</v>
+      </c>
+      <c r="B417" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C417" s="18" t="s">
+        <v>431</v>
+      </c>
+      <c r="D417" s="19">
+        <v>1330</v>
+      </c>
+      <c r="E417" s="19">
+        <v>0</v>
+      </c>
+      <c r="F417" s="19">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A418" s="13">
+        <v>52</v>
+      </c>
+      <c r="B418" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C418" s="22" t="s">
+        <v>432</v>
+      </c>
+      <c r="D418" s="23">
+        <v>5704</v>
+      </c>
+      <c r="E418" s="23">
+        <v>1922</v>
+      </c>
+      <c r="F418" s="23">
+        <v>7626</v>
+      </c>
+    </row>
+    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A419" s="1">
+        <v>1</v>
+      </c>
+      <c r="B419" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C419" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="D419" s="17">
+        <v>14958</v>
+      </c>
+      <c r="E419" s="17">
+        <v>0</v>
+      </c>
+      <c r="F419" s="17">
+        <v>14958</v>
+      </c>
+    </row>
+    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A420" s="1">
+        <v>2</v>
+      </c>
+      <c r="B420" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C420" s="20" t="s">
+        <v>435</v>
+      </c>
+      <c r="D420" s="21">
+        <v>33580</v>
+      </c>
+      <c r="E420" s="21">
+        <v>0</v>
+      </c>
+      <c r="F420" s="21">
+        <v>33580</v>
       </c>
     </row>
   </sheetData>
